--- a/ClosedXML.Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -72,172 +72,116 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
-  </x:numFmts>
-  <x:fonts count="2">
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="10">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1E90FF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF00CED1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA9A9A9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDEB887"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFCD5C5C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE9967A"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFF1493"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="10">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="10">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="10">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00CED1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEB887"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9967A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E90FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD5C5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF1493"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,7 +491,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -572,49 +516,49 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="2"/>
-      <x:c r="C4" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="s">
+      <x:c r="A4" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="4"/>
-      <x:c r="F5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="5" t="s">
+      <x:c r="A5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="2"/>
+      <x:c r="F5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
+      <x:c r="A6" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="7" t="s">
@@ -628,56 +572,56 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F7" s="8"/>
-      <x:c r="G7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="s">
+      <x:c r="A7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F7" s="5"/>
+      <x:c r="G7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="8"/>
-      <x:c r="B8" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="4"/>
+      <x:c r="A8" s="5"/>
+      <x:c r="B8" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="2"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
+      <x:c r="A9" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H9" s="9"/>
+      <x:c r="F9" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H9" s="8"/>
     </x:row>
     <x:row r="10" spans="1:8">
       <x:c r="A10" s="7" t="s">
@@ -689,29 +633,29 @@
       <x:c r="C10" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H10" s="6" t="s">
+      <x:c r="F10" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:8">
-      <x:c r="A11" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="9"/>
-      <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2" t="s">
+      <x:c r="A11" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" s="8"/>
+      <x:c r="F11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="1"/>
+      <x:c r="H11" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -735,147 +679,147 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E3" s="8"/>
-      <x:c r="F3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="9" t="s">
+      <x:c r="A3" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="14"/>
+      <x:c r="F3" s="15" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G3" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="17" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="2"/>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="s">
+      <x:c r="A4" s="10"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4"/>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
+      <x:c r="A5" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="11"/>
+      <x:c r="C5" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="9"/>
+      <x:c r="G5" s="16" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="17"/>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H8" s="8"/>
+      <x:c r="A8" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F8" s="17" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H8" s="14"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="8" t="s">
+      <x:c r="A9" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="10"/>
+      <x:c r="H9" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
+      <x:c r="A10" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F10" s="9"/>
-      <x:c r="G10" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="s">
+      <x:c r="D10" s="11"/>
+      <x:c r="E10" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -900,62 +844,62 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="A2" s="9" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="9" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="2"/>
-      <x:c r="C5" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="8"/>
-      <x:c r="G5" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="s">
+      <x:c r="A5" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="1"/>
+      <x:c r="C5" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="5"/>
+      <x:c r="G5" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="4"/>
-      <x:c r="F6" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="s">
+      <x:c r="A6" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="F6" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
+      <x:c r="A7" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
@@ -969,60 +913,60 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="A8" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="8"/>
-      <x:c r="B9" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="s">
+      <x:c r="A9" s="5"/>
+      <x:c r="B9" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
+      <x:c r="A10" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F10" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="4"/>
+      <x:c r="F10" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G10" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11" spans="1:8">
       <x:c r="A11" s="7" t="s">
@@ -1034,29 +978,29 @@
       <x:c r="C11" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="1"/>
+      <x:c r="H11" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:8">
-      <x:c r="A12" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="9"/>
-      <x:c r="F12" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G12" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H12" s="9"/>
+      <x:c r="A12" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="8"/>
+      <x:c r="F12" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H12" s="8"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1079,50 +1023,50 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2"/>
-      <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G3" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="9"/>
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="4"/>
-      <x:c r="F4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H4" s="4"/>
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="2"/>
+      <x:c r="F4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H4" s="2"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
@@ -1136,58 +1080,58 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F6" s="8"/>
-      <x:c r="G6" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="8" t="s">
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F6" s="5"/>
+      <x:c r="G6" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="8"/>
-      <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="s">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="A8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="F8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1201,29 +1145,29 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H9" s="6" t="s">
+      <x:c r="F9" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="9"/>
-      <x:c r="F10" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2" t="s">
+      <x:c r="A10" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="8"/>
+      <x:c r="F10" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="1"/>
+      <x:c r="H10" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1248,28 +1192,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="s">
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="6" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
@@ -1277,22 +1221,22 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="5"/>
-      <x:c r="D6" s="3" t="s">
+      <x:c r="A6" s="4"/>
+      <x:c r="D6" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
-      <x:c r="A7" s="8"/>
-      <x:c r="D7" s="4" t="s">
+      <x:c r="A7" s="5"/>
+      <x:c r="D7" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
-      <x:c r="A8" s="3" t="s">
+      <x:c r="A8" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1300,13 +1244,13 @@
       <x:c r="A9" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D9" s="5"/>
+      <x:c r="D9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:4">
-      <x:c r="A10" s="9" t="s">
+      <x:c r="A10" s="8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="8"/>
+      <x:c r="D10" s="5"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1329,36 +1273,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="2"/>
-      <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="s">
+      <x:c r="A3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="4"/>
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="2"/>
       <x:c r="F4" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1370,78 +1314,78 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="4"/>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="2"/>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="8"/>
-      <x:c r="B7" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="s">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H7" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="A8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="9"/>
+      <x:c r="F8" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="8"/>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="7" t="s">
@@ -1453,27 +1397,27 @@
       <x:c r="C9" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="2" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="1"/>
+      <x:c r="H9" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="9"/>
-      <x:c r="F10" s="8"/>
-      <x:c r="G10" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="s">
+      <x:c r="A10" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="8"/>
+      <x:c r="F10" s="5"/>
+      <x:c r="G10" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
